--- a/Stamboom anoniem.xlsx
+++ b/Stamboom anoniem.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fa0de5b2b0163307/Documenten/Leren/Anonieme kaart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="208" documentId="8_{8C0F98D5-8749-4119-A657-045C96555B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{756552E6-A0B3-454E-8B25-CED3E5A4EB2C}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="8_{8C0F98D5-8749-4119-A657-045C96555B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAF20A5E-1760-4F70-A89F-BA8A11CABAD2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{5EBBA593-250B-4B18-85DD-B5986749983C}"/>
   </bookViews>
@@ -234,133 +234,133 @@
     <t>Den Bosch</t>
   </si>
   <si>
-    <t>Lorenzo werd geboren in Rosenheim in het-jarige leeftijd 1650. Hij is overleden in 1697 op 47-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Bernhard werd geboren in Rosenheim in het-jarige leeftijd 1681. Hij is overleden in 1719 op 38-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Carmelo werd geboren in Seefeld in het-jarige leeftijd 1712. Hij is overleden in 1713 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Durante werd geboren in Seefeld in het-jarige leeftijd 1717. Hij is overleden in 1717 op 0-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Gianluca werd geboren in Karlsruhe in het-jarige leeftijd 1736. Hij is overleden in 1818 op 82-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Goyo werd geboren in Kaiserslautern in het-jarige leeftijd 1743. Hij is overleden in 1795 op 52-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Benjamin werd geboren in Kaiserslautern in het-jarige leeftijd 1735. Hij is overleden in 1748 op 13-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Ferdi werd geboren in Kaiserslautern in het-jarige leeftijd 1736. Hij is overleden in 1737 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Liberto werd geboren in Kaiserslautern in het-jarige leeftijd 1741. Hij is overleden in 1742 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Dave werd geboren in Kaiserslautern in het-jarige leeftijd 1745. Hij is overleden in 1746 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Bernd werd geboren in Morbach in het-jarige leeftijd 1760. Hij is overleden in 1761 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Kenneth werd geboren in Morbach in het-jarige leeftijd 1762. Hij is overleden in 1798 op 36-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Cipriano werd geboren in Morbach in het-jarige leeftijd 1767. Hij is overleden in 1768 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Ottavio werd geboren in Morbach in het-jarige leeftijd 1771. Hij is overleden in 1771 op 0-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Lope werd geboren in Bonn in het-jarige leeftijd 1765. Hij is overleden in 1824 op 59-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Pepijn werd geboren in Aken in het-jarige leeftijd 1803. Hij is overleden in 1876 op 73-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Dani werd geboren in Roermond in het-jarige leeftijd 1843. Hij is overleden in 1895 op 52-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Jasper werd geboren in Eindhoven in het-jarige leeftijd 1885. Hij is overleden in 1940 op 55-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Jose Ignacio werd geboren in Eindhoven in het-jarige leeftijd 1921. Hij is overleden in 1999 op 78-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Luigi werd geboren in Den Bosch in het-jarige leeftijd 1954. Hij is nu 71 jaar oud.</t>
-  </si>
-  <si>
-    <t>Febe werd geboren in Den Bosch in het-jarige leeftijd 1982. Hij is nu 43 jaar oud.</t>
-  </si>
-  <si>
-    <t>Gianfranco werd geboren in Utrecht in het-jarige leeftijd 1985. Hij is nu 40 jaar oud.</t>
-  </si>
-  <si>
-    <t>Klaas werd geboren in Utrecht in het-jarige leeftijd 1989. Hij is nu 36 jaar oud.</t>
-  </si>
-  <si>
-    <t>Ana Sofía werd geboren in Rosenheim in het-jarige leeftijd 1650. Zij is overleden in 1709 op 59-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Sophia werd geboren in Rosenheim in het-jarige leeftijd 1681. Zij is overleden in 1742 op 61-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Arnaldo werd geboren in Starnberg in het-jarige leeftijd 1713. Zij is overleden in 1772 op 59-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>María Carmen werd geboren in Starnberg in het-jarige leeftijd 1709. Zij is overleden in 1745 op 36-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Rosalia werd geboren in Starnberg in het-jarige leeftijd 1736. Zij is overleden in 1807 op 71-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Eliana werd geboren in Starnberg in het-jarige leeftijd 1709. Zij is overleden in 1709 op 0-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Anastasia werd geboren in Seefeld in het-jarige leeftijd 1719. Zij is overleden in 1719 op 0-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Charlotte werd geboren in Morbach in het-jarige leeftijd 1759. Zij is overleden in 1760 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Paloma werd geboren in Morbach in het-jarige leeftijd 1764. Zij is overleden in 1765 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Rosalina werd geboren in Morbach in het-jarige leeftijd 1770. Zij is overleden in 1772 op 2-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Luna werd geboren in Morbach in het-jarige leeftijd 1772. Zij is overleden in 1773 op 1-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Delia werd geboren in Bonn in het-jarige leeftijd 1782. Zij is overleden in 1843 op 61-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Corinna werd geboren in Aken in het-jarige leeftijd 1802. Zij is overleden in 1885 op 83-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Aline werd geboren in Roermond in het-jarige leeftijd 1845. Zij is overleden in 1919 op 74-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Graziella werd geboren in Eindhoven in het-jarige leeftijd 1884. Zij is overleden in 1939 op 55-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Jaqueline werd geboren in Eindhoven in het-jarige leeftijd 1930. Zij is overleden in 1988 op 58-jarige leeftijd.</t>
-  </si>
-  <si>
-    <t>Eleanora werd geboren in Den Bosch in het-jarige leeftijd 1956. Zij is nu 69 jaar oud.</t>
-  </si>
-  <si>
-    <t>Alma werd geboren in Utrecht in het-jarige leeftijd 1990. Zij is nu 35 jaar oud.</t>
-  </si>
-  <si>
-    <t>Katerina werd geboren in Utrecht in het-jarige leeftijd 1987. Zij is nu 38 jaar oud.</t>
-  </si>
-  <si>
-    <t>Natalija werd geboren in Utrecht in het-jarige leeftijd 1985. Zij is nu 40 jaar oud.</t>
+    <t>Lorenzo werd geboren in Rosenheim in 1650. Hij is overleden in 1697 op 47-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Ana Sofía werd geboren in Rosenheim in 1650. Zij is overleden in 1709 op 59-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Bernhard werd geboren in Rosenheim in 1681. Hij is overleden in 1719 op 38-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Sophia werd geboren in Rosenheim in 1681. Zij is overleden in 1742 op 61-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Arnaldo werd geboren in Starnberg in 1713. Zij is overleden in 1772 op 59-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>María Carmen werd geboren in Starnberg in 1709. Zij is overleden in 1745 op 36-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Rosalia werd geboren in Starnberg in 1736. Zij is overleden in 1807 op 71-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Eliana werd geboren in Starnberg in 1709. Zij is overleden in 1709 op 0-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Carmelo werd geboren in Seefeld in 1712. Hij is overleden in 1713 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Durante werd geboren in Seefeld in 1717. Hij is overleden in 1717 op 0-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Anastasia werd geboren in Seefeld in 1719. Zij is overleden in 1719 op 0-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Gianluca werd geboren in Karlsruhe in 1736. Hij is overleden in 1818 op 82-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Goyo werd geboren in Kaiserslautern in 1743. Hij is overleden in 1795 op 52-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Benjamin werd geboren in Kaiserslautern in 1735. Hij is overleden in 1748 op 13-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Ferdi werd geboren in Kaiserslautern in 1736. Hij is overleden in 1737 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Liberto werd geboren in Kaiserslautern in 1741. Hij is overleden in 1742 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Dave werd geboren in Kaiserslautern in 1745. Hij is overleden in 1746 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Charlotte werd geboren in Morbach in 1759. Zij is overleden in 1760 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Bernd werd geboren in Morbach in 1760. Hij is overleden in 1761 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Kenneth werd geboren in Morbach in 1762. Hij is overleden in 1798 op 36-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Paloma werd geboren in Morbach in 1764. Zij is overleden in 1765 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Cipriano werd geboren in Morbach in 1767. Hij is overleden in 1768 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Rosalina werd geboren in Morbach in 1770. Zij is overleden in 1772 op 2-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Ottavio werd geboren in Morbach in 1771. Hij is overleden in 1771 op 0-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Luna werd geboren in Morbach in 1772. Zij is overleden in 1773 op 1-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Lope werd geboren in Bonn in 1765. Hij is overleden in 1824 op 59-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Delia werd geboren in Bonn in 1782. Zij is overleden in 1843 op 61-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Pepijn werd geboren in Aken in 1803. Hij is overleden in 1876 op 73-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Corinna werd geboren in Aken in 1802. Zij is overleden in 1885 op 83-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Dani werd geboren in Roermond in 1843. Hij is overleden in 1895 op 52-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Aline werd geboren in Roermond in 1845. Zij is overleden in 1919 op 74-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Jasper werd geboren in Eindhoven in 1885. Hij is overleden in 1940 op 55-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Graziella werd geboren in Eindhoven in 1884. Zij is overleden in 1939 op 55-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Jose Ignacio werd geboren in Eindhoven in 1921. Hij is overleden in 1999 op 78-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Jaqueline werd geboren in Eindhoven in 1930. Zij is overleden in 1988 op 58-jarige leeftijd.</t>
+  </si>
+  <si>
+    <t>Luigi werd geboren in Den Bosch in 1954. Hij is nu 71 jaar oud.</t>
+  </si>
+  <si>
+    <t>Eleanora werd geboren in Den Bosch in 1956. Zij is nu 69 jaar oud.</t>
+  </si>
+  <si>
+    <t>Febe werd geboren in Den Bosch in 1982. Hij is nu 43 jaar oud.</t>
+  </si>
+  <si>
+    <t>Alma werd geboren in Utrecht in 1990. Zij is nu 35 jaar oud.</t>
+  </si>
+  <si>
+    <t>Gianfranco werd geboren in Utrecht in 1985. Hij is nu 40 jaar oud.</t>
+  </si>
+  <si>
+    <t>Katerina werd geboren in Utrecht in 1987. Zij is nu 38 jaar oud.</t>
+  </si>
+  <si>
+    <t>Klaas werd geboren in Utrecht in 1989. Hij is nu 36 jaar oud.</t>
+  </si>
+  <si>
+    <t>Natalija werd geboren in Utrecht in 1985. Zij is nu 40 jaar oud.</t>
   </si>
 </sst>
 </file>
@@ -412,7 +412,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -426,7 +426,6 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Komma" xfId="1" builtinId="3"/>
@@ -871,7 +870,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -909,7 +908,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -947,7 +946,7 @@
         <v>2</v>
       </c>
       <c r="L5" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -985,7 +984,7 @@
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1023,7 +1022,7 @@
         <v>3</v>
       </c>
       <c r="L7" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1061,7 +1060,7 @@
         <v>3</v>
       </c>
       <c r="L8" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1099,7 +1098,7 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1137,7 +1136,7 @@
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1175,7 +1174,7 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1213,7 +1212,7 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1251,7 +1250,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1289,7 +1288,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1327,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1365,7 +1364,7 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="N16" s="3"/>
     </row>
@@ -1382,7 +1381,7 @@
       <c r="D17">
         <v>1</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17">
@@ -1404,7 +1403,7 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1420,16 +1419,16 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18">
         <v>49.483586988665003</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18">
         <v>7.7773227303778096</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" t="s">
         <v>14</v>
       </c>
       <c r="I18" t="s">
@@ -1442,7 +1441,7 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="N18" s="3"/>
     </row>
@@ -1459,16 +1458,16 @@
       <c r="D19">
         <v>1</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19">
         <v>49.788507364960203</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19">
         <v>7.1100541690268502</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" t="s">
         <v>14</v>
       </c>
       <c r="I19" t="s">
@@ -1481,7 +1480,7 @@
         <v>4</v>
       </c>
       <c r="L19" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1497,16 +1496,16 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" t="s">
         <v>62</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20">
         <v>49.791634257229802</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20">
         <v>7.0783514949688904</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" t="s">
         <v>14</v>
       </c>
       <c r="I20" t="s">
@@ -1519,7 +1518,7 @@
         <v>4</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1535,16 +1534,16 @@
       <c r="D21">
         <v>36</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21">
         <v>49.816926234766498</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21">
         <v>7.0713064562893404</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" t="s">
         <v>14</v>
       </c>
       <c r="I21" t="s">
@@ -1557,7 +1556,7 @@
         <v>4</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1573,16 +1572,16 @@
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22">
         <v>49.811812069294703</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22">
         <v>7.1276667657257198</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" t="s">
         <v>14</v>
       </c>
       <c r="I22" t="s">
@@ -1595,7 +1594,7 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1611,7 +1610,7 @@
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" t="s">
         <v>62</v>
       </c>
       <c r="F23">
@@ -1633,7 +1632,7 @@
         <v>4</v>
       </c>
       <c r="L23" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1649,7 +1648,7 @@
       <c r="D24">
         <v>2</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" t="s">
         <v>62</v>
       </c>
       <c r="F24">
@@ -1671,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="L24" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1687,7 +1686,7 @@
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" t="s">
         <v>62</v>
       </c>
       <c r="F25">
@@ -1709,7 +1708,7 @@
         <v>4</v>
       </c>
       <c r="L25" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1725,7 +1724,7 @@
       <c r="D26">
         <v>1</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" t="s">
         <v>62</v>
       </c>
       <c r="F26">
@@ -1747,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="L26" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -1763,7 +1762,7 @@
       <c r="D27">
         <v>59</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" t="s">
         <v>63</v>
       </c>
       <c r="F27">
@@ -1785,7 +1784,7 @@
         <v>4</v>
       </c>
       <c r="L27" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -1823,7 +1822,7 @@
         <v>4</v>
       </c>
       <c r="L28" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -1861,7 +1860,7 @@
         <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -1899,7 +1898,7 @@
         <v>5</v>
       </c>
       <c r="L30" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -1937,7 +1936,7 @@
         <v>6</v>
       </c>
       <c r="L31" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="M31" s="4"/>
     </row>
@@ -1976,7 +1975,7 @@
         <v>6</v>
       </c>
       <c r="L32" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
@@ -2014,7 +2013,7 @@
         <v>7</v>
       </c>
       <c r="L33" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
@@ -2052,7 +2051,7 @@
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -2090,7 +2089,7 @@
         <v>8</v>
       </c>
       <c r="L35" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -2128,7 +2127,7 @@
         <v>8</v>
       </c>
       <c r="L36" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -2166,7 +2165,7 @@
         <v>9</v>
       </c>
       <c r="L37" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -2204,7 +2203,7 @@
         <v>9</v>
       </c>
       <c r="L38" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2242,7 +2241,7 @@
         <v>10</v>
       </c>
       <c r="L39" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2280,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="L40" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2318,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="L41" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2356,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="L42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -2394,7 +2393,7 @@
         <v>10</v>
       </c>
       <c r="L43" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
